--- a/Items.xlsx
+++ b/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
   <si>
     <t>Name</t>
   </si>
@@ -120,9 +120,6 @@
     <t>Red wooden barrel</t>
   </si>
   <si>
-    <t>Weak:Fire, Explosive</t>
-  </si>
-  <si>
     <t>Toxic barrel</t>
   </si>
   <si>
@@ -136,6 +133,21 @@
   </si>
   <si>
     <t>Not enough tests</t>
+  </si>
+  <si>
+    <t>Lightning rod</t>
+  </si>
+  <si>
+    <t>Places 1 Lightning rod</t>
+  </si>
+  <si>
+    <t>Metallic stick</t>
+  </si>
+  <si>
+    <t>Conductive, Unscoring</t>
+  </si>
+  <si>
+    <t>Vulnerable:Fire, Explosive, Unscoring</t>
   </si>
 </sst>
 </file>
@@ -276,7 +288,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,9 +303,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
@@ -311,25 +320,31 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -638,696 +653,764 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M58"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="4"/>
-    <col min="3" max="3" width="16.28515625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="36.85546875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.42578125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" style="4"/>
-    <col min="13" max="13" width="5.140625" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="8.85546875" style="4"/>
+    <col min="1" max="2" width="8.88671875" style="4"/>
+    <col min="3" max="3" width="16.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="8.44140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="4"/>
+    <col min="13" max="13" width="5.109375" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="5"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G1" s="13"/>
+    </row>
+    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="5"/>
+      <c r="F5" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:13" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="8" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="5"/>
+      <c r="F8" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="C9"/>
       <c r="D9"/>
-      <c r="E9" s="6"/>
+      <c r="E9" s="5"/>
       <c r="F9"/>
       <c r="G9"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="7" t="s">
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="C10" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="5"/>
+      <c r="F10" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
     </row>
     <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="9" t="s">
+      <c r="E11" s="5"/>
+      <c r="F11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="7" t="s">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="E12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="C13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="15" t="s">
+      <c r="E13" s="5"/>
+      <c r="F13" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="L13" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M13" s="15" t="s">
+      <c r="M13" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="C14" s="12" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C14" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="15" t="s">
+      <c r="E14" s="5"/>
+      <c r="F14" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="12">
         <v>2</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="12">
         <v>0</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K14" s="15" t="s">
+      <c r="K14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="L14" s="15" t="s">
+      <c r="L14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="15" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="18"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="F16" s="15" t="s">
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="16"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="F16" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="18"/>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G16" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="16"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C17"/>
       <c r="D17"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="7" t="s">
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="3:13" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="14" t="s">
+      <c r="E19" s="5"/>
+      <c r="F19" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="3:13" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="G18" s="14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="C19" s="7" t="s">
+      <c r="D21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="E21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C22"/>
-      <c r="D22"/>
+      <c r="D22" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="E23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-    </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-    </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-    </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-    </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-    </row>
-    <row r="33" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="3:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-    </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-    </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-    </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-    </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-    </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-    </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-    </row>
-    <row r="41" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-    </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-    </row>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-    </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-    </row>
-    <row r="45" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-    </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-    </row>
-    <row r="47" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-    </row>
-    <row r="48" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-    </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-    </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-    </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-    </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-    </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-    </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-    </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-    </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-    </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-    </row>
-    <row r="58" spans="3:10" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
+      <c r="F22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="E23" s="5"/>
+      <c r="F23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+    </row>
+    <row r="33" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+    </row>
+    <row r="34" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+    </row>
+    <row r="35" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+    </row>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+    </row>
+    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+    </row>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+    </row>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+    </row>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+    </row>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+    </row>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+    </row>
+    <row r="45" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+    </row>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+    </row>
+    <row r="47" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+    </row>
+    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+    </row>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+    </row>
+    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+    </row>
+    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+    </row>
+    <row r="58" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="G23:M23"/>
+    <mergeCell ref="G24:M24"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="G15:M15"/>
@@ -1336,15 +1419,16 @@
     <mergeCell ref="D14:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1354,7 +1438,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
   <si>
     <t>Name</t>
   </si>
@@ -45,18 +45,12 @@
     <t>Covers 3x3 square in Water</t>
   </si>
   <si>
-    <t>Covers</t>
-  </si>
-  <si>
     <t>Water</t>
   </si>
   <si>
     <t>Ice</t>
   </si>
   <si>
-    <t xml:space="preserve">Applies: Resistance:Fire, Weak:Lightning, If attacked by (Frost) damage, converts to Ice </t>
-  </si>
-  <si>
     <t>Applies: Resistance:Fire, Slippery. If attacked by (Fire) damage, converts to water</t>
   </si>
   <si>
@@ -148,6 +142,81 @@
   </si>
   <si>
     <t>Vulnerable:Fire, Explosive, Unscoring</t>
+  </si>
+  <si>
+    <t>Applies: Resistance:Fire, Weak:Lightning, If attacked by (Frost) damage, converts to Ice.  If attacked by (Fire) damage, disappears</t>
+  </si>
+  <si>
+    <t>Small war hammer</t>
+  </si>
+  <si>
+    <t>Instantly destroys selected unit</t>
+  </si>
+  <si>
+    <t>Origami</t>
+  </si>
+  <si>
+    <t>Additional info</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Gains Vulnerable:Fire and Fragile, looses Resistant:Fire, has 1 less maximum health (To a minimum of 1)</t>
+  </si>
+  <si>
+    <t>Master bolt</t>
+  </si>
+  <si>
+    <t>Storm clouds</t>
+  </si>
+  <si>
+    <t>Covers 1 cell in Storm clouds</t>
+  </si>
+  <si>
+    <t>At the end of the turn, deals 3 (Lightning damage) to units on top</t>
+  </si>
+  <si>
+    <t>A critical roll</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>1, normal</t>
+  </si>
+  <si>
+    <t>Place a "Dice mimic" anywhere on the battlefield</t>
+  </si>
+  <si>
+    <t>Dice mimic</t>
+  </si>
+  <si>
+    <t>Big green dice with sharp teeth and long tongue</t>
+  </si>
+  <si>
+    <t>Randomized</t>
+  </si>
+  <si>
+    <t>Create a copy of selected unit made out of Paper and place it 2 cells away from the original</t>
+  </si>
+  <si>
+    <t>Blood stew</t>
+  </si>
+  <si>
+    <t>Selected unit gains "Strengthened" and "Exposed"</t>
+  </si>
+  <si>
+    <t>D4                                                                           (Physical, Fire, Lightning, Frost)</t>
+  </si>
+  <si>
+    <t>Polymorph hex</t>
+  </si>
+  <si>
+    <t>Applies "Polymorphed" to selected unit</t>
   </si>
 </sst>
 </file>
@@ -220,7 +289,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -280,6 +349,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -288,7 +366,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -326,6 +404,21 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -342,9 +435,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -655,35 +745,41 @@
   <dimension ref="A1:M58"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="4"/>
-    <col min="3" max="3" width="16.33203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="4"/>
+    <col min="2" max="2" width="5" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="3.88671875" style="4" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="36.88671875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="46.21875" style="4" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="8.44140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="40.44140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="32.44140625" style="4" customWidth="1"/>
     <col min="11" max="11" width="12.44140625" style="4" customWidth="1"/>
     <col min="12" max="12" width="8.88671875" style="4"/>
     <col min="13" max="13" width="5.109375" style="4" customWidth="1"/>
     <col min="14" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="13"/>
-    </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -698,13 +794,17 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-    </row>
-    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -718,23 +818,27 @@
       <c r="F5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-    </row>
-    <row r="6" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5"/>
+      <c r="I5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -742,38 +846,38 @@
         <v>0</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>15</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9" s="5"/>
@@ -783,43 +887,31 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>16</v>
-      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -830,44 +922,44 @@
         <v>0</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="12" t="s">
         <v>0</v>
       </c>
       <c r="G13" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="J13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="K13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="L13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="M13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L13" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" s="12" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>21</v>
+      <c r="C14" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>19</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G14" s="12">
         <v>2</v>
@@ -876,53 +968,53 @@
         <v>0</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K14" s="12" t="s">
-        <v>32</v>
-      </c>
       <c r="L14" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M14" s="12">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="5"/>
       <c r="F15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="16"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="21"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="23"/>
       <c r="F16" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="16"/>
+      <c r="G16" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="21"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C17"/>
@@ -934,14 +1026,14 @@
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="11" t="s">
         <v>0</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -949,14 +1041,14 @@
         <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="11" t="s">
         <v>6</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.3">
@@ -974,44 +1066,44 @@
         <v>0</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>40</v>
+      <c r="C22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G22" s="3">
         <v>1</v>
@@ -1020,52 +1112,54 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="L22" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M22" s="3">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
       <c r="E23" s="5"/>
       <c r="F23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
+        <v>29</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
       <c r="E24" s="5"/>
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
+      <c r="G24" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C25" s="5"/>
@@ -1078,8 +1172,12 @@
       <c r="J25" s="5"/>
     </row>
     <row r="26" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -1088,8 +1186,12 @@
       <c r="J26" s="5"/>
     </row>
     <row r="27" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>44</v>
+      </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -1098,8 +1200,8 @@
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -1108,8 +1210,8 @@
       <c r="J28" s="5"/>
     </row>
     <row r="29" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -1128,46 +1230,62 @@
       <c r="J30" s="5"/>
     </row>
     <row r="31" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="F31" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
     </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+    <row r="32" spans="3:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>61</v>
+      </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
+      <c r="F32" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>48</v>
+      </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
     </row>
-    <row r="33" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
+    <row r="33" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
       <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
     </row>
-    <row r="34" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
+    <row r="34" spans="3:13" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
       <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
     </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -1177,47 +1295,63 @@
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
     </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
+    <row r="36" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C36" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
+      <c r="F36" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
     </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
+    <row r="37" spans="3:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+      <c r="F37" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>52</v>
+      </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
     </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
+    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C38" s="16"/>
+      <c r="D38" s="17"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
     </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
+    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C39" s="16"/>
+      <c r="D39" s="17"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
     </row>
-    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -1227,47 +1361,107 @@
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
     </row>
-    <row r="41" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
+    <row r="41" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C41" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-    </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
+      <c r="F41" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C42" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>57</v>
+      </c>
       <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-    </row>
-    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
+      <c r="F42" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C43" s="16"/>
+      <c r="D43" s="17"/>
       <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-    </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
+      <c r="F43" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+    </row>
+    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C44" s="16"/>
+      <c r="D44" s="17"/>
       <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-    </row>
-    <row r="45" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F44" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+    </row>
+    <row r="45" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -1277,9 +1471,13 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
     </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
+    <row r="46" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C46" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>62</v>
+      </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -1287,9 +1485,13 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
     </row>
-    <row r="47" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
+    <row r="47" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C47" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>63</v>
+      </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -1297,9 +1499,9 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
     </row>
-    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
+    <row r="48" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C48" s="16"/>
+      <c r="D48" s="17"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -1308,8 +1510,8 @@
       <c r="J48" s="5"/>
     </row>
     <row r="49" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="17"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -1328,8 +1530,12 @@
       <c r="J50" s="5"/>
     </row>
     <row r="51" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
+      <c r="C51" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>65</v>
+      </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -1338,8 +1544,12 @@
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
+      <c r="C52" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>66</v>
+      </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -1348,8 +1558,8 @@
       <c r="J52" s="5"/>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="17"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -1358,8 +1568,8 @@
       <c r="J53" s="5"/>
     </row>
     <row r="54" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="17"/>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -1408,15 +1618,35 @@
       <c r="J58" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="28">
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="F1:L1"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
     <mergeCell ref="G23:M23"/>
     <mergeCell ref="G24:M24"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:G1"/>
     <mergeCell ref="G15:M15"/>
     <mergeCell ref="G16:M16"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="D14:D16"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="G43:M43"/>
+    <mergeCell ref="G44:M44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
   <si>
     <t>Name</t>
   </si>
@@ -150,21 +150,9 @@
     <t>Small war hammer</t>
   </si>
   <si>
-    <t>Instantly destroys selected unit</t>
-  </si>
-  <si>
-    <t>Origami</t>
-  </si>
-  <si>
     <t>Additional info</t>
   </si>
   <si>
-    <t>Paper</t>
-  </si>
-  <si>
-    <t>Gains Vulnerable:Fire and Fragile, looses Resistant:Fire, has 1 less maximum health (To a minimum of 1)</t>
-  </si>
-  <si>
     <t>Master bolt</t>
   </si>
   <si>
@@ -174,9 +162,6 @@
     <t>Covers 1 cell in Storm clouds</t>
   </si>
   <si>
-    <t>At the end of the turn, deals 3 (Lightning damage) to units on top</t>
-  </si>
-  <si>
     <t>A critical roll</t>
   </si>
   <si>
@@ -201,9 +186,6 @@
     <t>Randomized</t>
   </si>
   <si>
-    <t>Create a copy of selected unit made out of Paper and place it 2 cells away from the original</t>
-  </si>
-  <si>
     <t>Blood stew</t>
   </si>
   <si>
@@ -217,6 +199,12 @@
   </si>
   <si>
     <t>Applies "Polymorphed" to selected unit</t>
+  </si>
+  <si>
+    <t>Deal 3 (Physical) damage to the target</t>
+  </si>
+  <si>
+    <t>At the end of the round, deals 3 (Lightning damage) to units on top</t>
   </si>
 </sst>
 </file>
@@ -366,7 +354,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -422,6 +410,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -437,6 +434,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Вывод" xfId="3" builtinId="21"/>
@@ -743,43 +750,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M58"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="8.85546875" style="4"/>
     <col min="2" max="2" width="5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="25.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="3.88671875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="46.21875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="40.44140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="32.44140625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" style="4"/>
-    <col min="13" max="13" width="5.109375" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="4"/>
+    <col min="3" max="3" width="7.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="46.28515625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="40.42578125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="32.42578125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" style="4"/>
+    <col min="13" max="13" width="5.140625" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+    </row>
+    <row r="4" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -804,7 +811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -838,7 +845,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -859,7 +866,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
         <v>6</v>
       </c>
@@ -877,7 +884,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9" s="5"/>
@@ -887,7 +894,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C10" s="6" t="s">
         <v>0</v>
       </c>
@@ -899,7 +906,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="28.9" x14ac:dyDescent="0.3">
       <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
@@ -911,13 +918,13 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="E12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C13" s="6" t="s">
         <v>0</v>
       </c>
@@ -950,11 +957,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="22" t="s">
+    <row r="14" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C14" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="26" t="s">
         <v>19</v>
       </c>
       <c r="E14" s="5"/>
@@ -983,40 +990,40 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C15" s="25"/>
+      <c r="D15" s="26"/>
       <c r="E15" s="5"/>
       <c r="F15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="21"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C16" s="22"/>
-      <c r="D16" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="24"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C16" s="25"/>
+      <c r="D16" s="26"/>
       <c r="F16" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="21"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="24"/>
+    </row>
+    <row r="17" spans="3:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17" s="5"/>
@@ -1036,7 +1043,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:13" ht="30" x14ac:dyDescent="0.25">
       <c r="C19" s="6" t="s">
         <v>6</v>
       </c>
@@ -1051,7 +1058,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1061,107 +1068,107 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="3:13" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7" t="s">
+    <row r="21" spans="3:13" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="E21" s="27"/>
+      <c r="F21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="L21" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="M21" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="16" t="s">
+    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="E22"/>
-      <c r="F22" s="3" t="s">
+      <c r="E22" s="30"/>
+      <c r="F22" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="12">
         <v>1</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="H22" s="12">
+        <v>0</v>
+      </c>
+      <c r="I22" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="L22" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C23" s="16"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="3" t="s">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C23" s="28"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="17" t="s">
+      <c r="G23" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C24" s="16"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="3" t="s">
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C24" s="28"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+    </row>
+    <row r="25" spans="3:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1171,11 +1178,11 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C26" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7" t="s">
+    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C26" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>43</v>
       </c>
       <c r="E26" s="5"/>
@@ -1185,12 +1192,12 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C27" s="16" t="s">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C27" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>44</v>
+      <c r="D27" s="29" t="s">
+        <v>61</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1199,9 +1206,9 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C28" s="16"/>
-      <c r="D28" s="17"/>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C28" s="28"/>
+      <c r="D28" s="29"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -1209,9 +1216,9 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C29" s="16"/>
-      <c r="D29" s="17"/>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C29" s="28"/>
+      <c r="D29" s="29"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -1219,7 +1226,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -1229,43 +1236,49 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C31" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="7" t="s">
+    <row r="31" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C31" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="16" t="s">
         <v>45</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>47</v>
+      <c r="F31" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
-    </row>
-    <row r="32" spans="3:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+    </row>
+    <row r="32" spans="3:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="16" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
-    </row>
-    <row r="33" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+    </row>
+    <row r="33" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="16"/>
       <c r="D33" s="17"/>
       <c r="E33" s="5"/>
@@ -1274,8 +1287,11 @@
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
-    </row>
-    <row r="34" spans="3:13" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+    </row>
+    <row r="34" spans="3:13" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="16"/>
       <c r="D34" s="17"/>
       <c r="E34" s="5"/>
@@ -1284,8 +1300,11 @@
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
-    </row>
-    <row r="35" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+    </row>
+    <row r="35" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -1294,64 +1313,111 @@
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
-    </row>
-    <row r="36" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C36" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>49</v>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+    </row>
+    <row r="36" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-    </row>
-    <row r="37" spans="3:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F36" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="3:13" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="16" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="K37" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-    </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="L37" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="M37" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C38" s="16"/>
       <c r="D38" s="17"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-    </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="F38" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+    </row>
+    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C39" s="16"/>
       <c r="D39" s="17"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-    </row>
-    <row r="40" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="F39" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+    </row>
+    <row r="40" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -1360,41 +1426,28 @@
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
-    </row>
-    <row r="41" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C41" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>53</v>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+    </row>
+    <row r="41" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="E41" s="5"/>
-      <c r="F41" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J41" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="K41" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L41" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M41" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+    </row>
+    <row r="42" spans="3:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="16" t="s">
         <v>6</v>
       </c>
@@ -1402,66 +1455,42 @@
         <v>57</v>
       </c>
       <c r="E42" s="5"/>
-      <c r="F42" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="J42" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K42" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="L42" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="M42" s="13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+    </row>
+    <row r="43" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C43" s="16"/>
       <c r="D43" s="17"/>
       <c r="E43" s="5"/>
-      <c r="F43" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G43" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-    </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+    </row>
+    <row r="44" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C44" s="16"/>
       <c r="D44" s="17"/>
       <c r="E44" s="5"/>
-      <c r="F44" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-    </row>
-    <row r="45" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+    </row>
+    <row r="45" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -1471,12 +1500,12 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
     </row>
-    <row r="46" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="14" t="s">
         <v>0</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -1485,12 +1514,12 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
     </row>
-    <row r="47" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C47" s="16" t="s">
+    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D47" s="17" t="s">
-        <v>63</v>
+      <c r="D47" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -1499,9 +1528,9 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
     </row>
-    <row r="48" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C48" s="16"/>
-      <c r="D48" s="17"/>
+    <row r="48" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C48" s="19"/>
+      <c r="D48" s="20"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -1509,9 +1538,9 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
     </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C49" s="16"/>
-      <c r="D49" s="17"/>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C49" s="19"/>
+      <c r="D49" s="20"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -1519,65 +1548,7 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-    </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C51" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-    </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C52" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-    </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C53" s="16"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-    </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-    </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -1587,7 +1558,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
     </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -1597,7 +1568,7 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
     </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -1607,7 +1578,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
     </row>
-    <row r="58" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:10" ht="55.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -1618,35 +1589,21 @@
       <c r="J58" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="F1:L1"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="G23:M23"/>
-    <mergeCell ref="G24:M24"/>
+  <mergeCells count="14">
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C22:C24"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G15:M15"/>
     <mergeCell ref="G16:M16"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="D14:D16"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="F37:F39"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="G43:M43"/>
-    <mergeCell ref="G44:M44"/>
+    <mergeCell ref="F1:L1"/>
+    <mergeCell ref="G23:M23"/>
+    <mergeCell ref="G24:M24"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1656,9 +1613,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1668,7 +1625,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -204,7 +204,7 @@
     <t>Deal 3 (Physical) damage to the target</t>
   </si>
   <si>
-    <t>At the end of the round, deals 3 (Lightning damage) to units on top</t>
+    <t>At the end of the round, deals 3 (Lightning) damage to units on top</t>
   </si>
 </sst>
 </file>
@@ -277,7 +277,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -344,6 +344,43 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -354,7 +391,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -395,26 +432,32 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -434,16 +477,24 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Вывод" xfId="3" builtinId="21"/>
@@ -750,43 +801,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M58"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="4"/>
+    <col min="1" max="1" width="8.88671875" style="4"/>
     <col min="2" max="2" width="5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="46.28515625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="40.42578125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="32.42578125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" style="4"/>
-    <col min="13" max="13" width="5.140625" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="8.85546875" style="4"/>
+    <col min="3" max="3" width="7.88671875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="46.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="40.44140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="32.44140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="4"/>
+    <col min="13" max="13" width="5.109375" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-    </row>
-    <row r="4" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -811,7 +862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -825,7 +876,7 @@
       <c r="F5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>42</v>
       </c>
       <c r="H5"/>
@@ -845,7 +896,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -866,7 +917,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
         <v>6</v>
       </c>
@@ -884,7 +935,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9" s="5"/>
@@ -894,7 +945,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C10" s="6" t="s">
         <v>0</v>
       </c>
@@ -906,7 +957,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="28.95" x14ac:dyDescent="0.3">
       <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
@@ -918,13 +969,13 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="C13" s="6" t="s">
         <v>0</v>
       </c>
@@ -957,11 +1008,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="C14" s="25" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C14" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="28" t="s">
         <v>19</v>
       </c>
       <c r="E14" s="5"/>
@@ -990,40 +1041,40 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="25"/>
-      <c r="D15" s="26"/>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
       <c r="E15" s="5"/>
       <c r="F15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="24"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="25"/>
-      <c r="D16" s="26"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="26"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
       <c r="F16" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="24"/>
-    </row>
-    <row r="17" spans="3:13" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="26"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17" s="5"/>
@@ -1036,14 +1087,14 @@
         <v>32</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="11" t="s">
+      <c r="F18" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="3:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C19" s="6" t="s">
         <v>6</v>
       </c>
@@ -1051,14 +1102,14 @@
         <v>33</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="3:13" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1068,14 +1119,14 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="3:13" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:13" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="27"/>
+      <c r="E21"/>
       <c r="F21" s="12" t="s">
         <v>0</v>
       </c>
@@ -1101,14 +1152,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="28" t="s">
+    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="30"/>
+      <c r="E22"/>
       <c r="F22" s="12" t="s">
         <v>37</v>
       </c>
@@ -1134,41 +1185,41 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="27"/>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C23" s="22"/>
+      <c r="D23" s="21"/>
+      <c r="E23"/>
       <c r="F23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="28"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="27"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="21"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C24" s="22"/>
+      <c r="D24" s="21"/>
+      <c r="E24"/>
       <c r="F24" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="29" t="s">
+      <c r="G24" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-    </row>
-    <row r="25" spans="3:13" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1178,7 +1229,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:13" ht="15" x14ac:dyDescent="0.25">
       <c r="C26" s="11" t="s">
         <v>0</v>
       </c>
@@ -1192,11 +1243,11 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C27" s="28" t="s">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C27" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="21" t="s">
         <v>61</v>
       </c>
       <c r="E27" s="5"/>
@@ -1206,9 +1257,9 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C28" s="22"/>
+      <c r="D28" s="21"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -1216,9 +1267,9 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C29" s="28"/>
-      <c r="D29" s="29"/>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C29" s="22"/>
+      <c r="D29" s="21"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -1226,7 +1277,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:13" ht="15" x14ac:dyDescent="0.25">
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -1236,67 +1287,67 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C31" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="16" t="s">
+    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C31" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="19" t="s">
         <v>45</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" s="16" t="s">
+      <c r="F31" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="19" t="s">
         <v>46</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-    </row>
-    <row r="32" spans="3:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="16" t="s">
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+    </row>
+    <row r="32" spans="3:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="20" t="s">
         <v>47</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" s="20" t="s">
         <v>62</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-    </row>
-    <row r="33" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="16"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="17"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+    </row>
+    <row r="33" spans="3:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-    </row>
-    <row r="34" spans="3:13" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="17"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+    </row>
+    <row r="34" spans="3:13" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
@@ -1304,7 +1355,7 @@
       <c r="L34" s="18"/>
       <c r="M34" s="18"/>
     </row>
-    <row r="35" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -1317,7 +1368,7 @@
       <c r="L35" s="18"/>
       <c r="M35" s="18"/>
     </row>
-    <row r="36" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="16" t="s">
         <v>0</v>
       </c>
@@ -1350,7 +1401,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="3:13" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:13" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="16" t="s">
         <v>6</v>
       </c>
@@ -1383,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C38" s="16"/>
       <c r="D38" s="17"/>
       <c r="E38" s="5"/>
@@ -1400,7 +1451,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
     </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C39" s="16"/>
       <c r="D39" s="17"/>
       <c r="E39" s="5"/>
@@ -1417,7 +1468,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
     </row>
-    <row r="40" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -1430,7 +1481,7 @@
       <c r="L40" s="18"/>
       <c r="M40" s="18"/>
     </row>
-    <row r="41" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="16" t="s">
         <v>0</v>
       </c>
@@ -1447,7 +1498,7 @@
       <c r="L41" s="18"/>
       <c r="M41" s="18"/>
     </row>
-    <row r="42" spans="3:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="16" t="s">
         <v>6</v>
       </c>
@@ -1464,7 +1515,7 @@
       <c r="L42" s="18"/>
       <c r="M42" s="18"/>
     </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C43" s="16"/>
       <c r="D43" s="17"/>
       <c r="E43" s="5"/>
@@ -1477,7 +1528,7 @@
       <c r="L43" s="18"/>
       <c r="M43" s="18"/>
     </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C44" s="16"/>
       <c r="D44" s="17"/>
       <c r="E44" s="5"/>
@@ -1490,7 +1541,7 @@
       <c r="L44" s="18"/>
       <c r="M44" s="18"/>
     </row>
-    <row r="45" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -1499,12 +1550,15 @@
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
-    </row>
-    <row r="46" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="14" t="s">
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+    </row>
+    <row r="46" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E46" s="5"/>
@@ -1513,12 +1567,15 @@
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
-    </row>
-    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="19" t="s">
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+    </row>
+    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="29" t="s">
         <v>60</v>
       </c>
       <c r="E47" s="5"/>
@@ -1527,20 +1584,26 @@
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
-    </row>
-    <row r="48" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C48" s="19"/>
-      <c r="D48" s="20"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+    </row>
+    <row r="48" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C48" s="33"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
-    </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C49" s="19"/>
-      <c r="D49" s="20"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C49" s="34"/>
+      <c r="D49" s="31"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -1548,7 +1611,7 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -1558,7 +1621,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
     </row>
-    <row r="56" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -1568,7 +1631,7 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
     </row>
-    <row r="57" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -1578,7 +1641,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
     </row>
-    <row r="58" spans="3:10" ht="55.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -1590,6 +1653,10 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
     <mergeCell ref="D22:D24"/>
     <mergeCell ref="C22:C24"/>
     <mergeCell ref="A1:E1"/>
@@ -1600,10 +1667,6 @@
     <mergeCell ref="F1:L1"/>
     <mergeCell ref="G23:M23"/>
     <mergeCell ref="G24:M24"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1613,9 +1676,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1625,7 +1688,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="73">
   <si>
     <t>Name</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Cursed card</t>
   </si>
   <si>
-    <t>Applies Exposed to selected unit</t>
-  </si>
-  <si>
     <t>Explosive barrel</t>
   </si>
   <si>
@@ -205,6 +202,39 @@
   </si>
   <si>
     <t>At the end of the round, deals 3 (Lightning) damage to units on top</t>
+  </si>
+  <si>
+    <t>Applies "Exposed" to selected unit</t>
+  </si>
+  <si>
+    <t>Crystal of blood</t>
+  </si>
+  <si>
+    <t>Applies "Bloodthirsty" to all units in a 3x3 square</t>
+  </si>
+  <si>
+    <t>Mida's paw</t>
+  </si>
+  <si>
+    <t>Turn 1 friendly unit into pure gold, permanently removing it from your army and receiving 5$</t>
+  </si>
+  <si>
+    <t>Bag of Mist</t>
+  </si>
+  <si>
+    <t>Cover a 3x3 square in Mist</t>
+  </si>
+  <si>
+    <t>Mist</t>
+  </si>
+  <si>
+    <t>Units wholly OUTSIDE the mist without "Penetrating" cannot damage any units wholly WITHIN the mist and wise versa. Lasts for 2 rounds</t>
+  </si>
+  <si>
+    <t>Turtle stew</t>
+  </si>
+  <si>
+    <t>Applies "Protected" and "Enfeebled"</t>
   </si>
 </sst>
 </file>
@@ -277,7 +307,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -346,43 +376,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -391,7 +384,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -432,9 +425,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -453,22 +443,31 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
@@ -477,22 +476,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -820,22 +804,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -848,10 +832,10 @@
         <v>7</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="5"/>
@@ -873,11 +857,11 @@
         <v>8</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>42</v>
+      <c r="F5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>41</v>
       </c>
       <c r="H5"/>
       <c r="I5" s="7" t="s">
@@ -889,7 +873,7 @@
     </row>
     <row r="6" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="5"/>
       <c r="H6" s="5"/>
@@ -957,12 +941,12 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="28.95" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="E11" s="5"/>
       <c r="H11" s="5"/>
@@ -975,104 +959,104 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C13" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C14" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="12" t="s">
+      <c r="E14" s="5"/>
+      <c r="F14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="9">
+        <v>2</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="12">
-        <v>2</v>
-      </c>
-      <c r="H14" s="12">
-        <v>0</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="J14" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="K14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C15" s="29"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="G15" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="L14" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="26"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="28"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="F16" s="12" t="s">
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
+      <c r="F16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="26"/>
+      <c r="G16" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="28"/>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C17"/>
@@ -1084,14 +1068,14 @@
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1099,14 +1083,14 @@
         <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.3">
@@ -1124,44 +1108,44 @@
         <v>0</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="12" t="s">
         <v>0</v>
       </c>
       <c r="G21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="I21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="J21" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="K21" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="L21" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="12" t="s">
+      <c r="M21" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="M21" s="12" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" s="12">
         <v>1</v>
@@ -1170,30 +1154,30 @@
         <v>0</v>
       </c>
       <c r="I22" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J22" s="12" t="s">
-        <v>28</v>
-      </c>
       <c r="K22" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M22" s="12">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C23" s="22"/>
+      <c r="C23" s="31"/>
       <c r="D23" s="21"/>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="21"/>
@@ -1203,14 +1187,14 @@
       <c r="M23" s="21"/>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C24" s="22"/>
+      <c r="C24" s="31"/>
       <c r="D24" s="21"/>
       <c r="E24"/>
       <c r="F24" s="12" t="s">
         <v>4</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="21"/>
@@ -1234,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -1244,11 +1228,11 @@
       <c r="J26" s="5"/>
     </row>
     <row r="27" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1258,7 +1242,7 @@
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C28" s="22"/>
+      <c r="C28" s="31"/>
       <c r="D28" s="21"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -1268,7 +1252,7 @@
       <c r="J28" s="5"/>
     </row>
     <row r="29" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C29" s="22"/>
+      <c r="C29" s="31"/>
       <c r="D29" s="21"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -1288,46 +1272,46 @@
       <c r="J30" s="5"/>
     </row>
     <row r="31" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C31" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="19" t="s">
+      <c r="C31" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="18" t="s">
         <v>45</v>
-      </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
     </row>
     <row r="32" spans="3:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>47</v>
+      <c r="C32" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>46</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" s="20" t="s">
-        <v>62</v>
+      <c r="F32" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>61</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
     </row>
     <row r="33" spans="3:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33"/>
@@ -1338,9 +1322,9 @@
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
     </row>
     <row r="34" spans="3:13" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34"/>
@@ -1351,9 +1335,9 @@
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
     </row>
     <row r="35" spans="3:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="5"/>
@@ -1364,109 +1348,109 @@
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
     </row>
     <row r="36" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36" s="16" t="s">
+      <c r="C36" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="3:13" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="G36" s="17" t="s">
+      <c r="H37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="J37" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16">
         <v>20</v>
       </c>
-      <c r="H36" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="L36" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="3:13" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="17" t="s">
+    </row>
+    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C38" s="15"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="G37" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="I37" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="J37" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="K37" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="L37" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="M37" s="17">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C38" s="16"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="G38" s="17" t="s">
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="24"/>
+    </row>
+    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C39" s="15"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-    </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C39" s="16"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="24"/>
     </row>
     <row r="40" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="5"/>
@@ -1477,16 +1461,16 @@
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
     </row>
     <row r="41" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>56</v>
+      <c r="C41" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>55</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -1494,16 +1478,16 @@
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
-    </row>
-    <row r="42" spans="3:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>57</v>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+    </row>
+    <row r="42" spans="3:13" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -1511,72 +1495,76 @@
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
     </row>
     <row r="43" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C43" s="16"/>
-      <c r="D43" s="17"/>
+      <c r="C43"/>
+      <c r="D43"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="18"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C44" s="16"/>
-      <c r="D44" s="17"/>
+      <c r="C44" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>58</v>
+      </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-    </row>
-    <row r="45" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+    </row>
+    <row r="45" spans="3:13" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
     </row>
     <row r="46" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>59</v>
-      </c>
+      <c r="C46"/>
+      <c r="D46"/>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
-      <c r="K46" s="18"/>
-      <c r="L46" s="18"/>
-      <c r="M46" s="18"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
     </row>
     <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="29" t="s">
-        <v>60</v>
+      <c r="C47" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -1584,32 +1572,78 @@
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
-      <c r="K47" s="18"/>
-      <c r="L47" s="18"/>
-      <c r="M47" s="18"/>
-    </row>
-    <row r="48" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C48" s="33"/>
-      <c r="D48" s="30"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+    </row>
+    <row r="48" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C48" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
-      <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
-      <c r="M48" s="18"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
     </row>
     <row r="49" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C49" s="34"/>
-      <c r="D49" s="31"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
+    </row>
+    <row r="50" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C50" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C51" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C53" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="55" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C55" s="5"/>
@@ -1622,8 +1656,12 @@
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
+      <c r="C56" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>71</v>
+      </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -1631,9 +1669,13 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
     </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
+    <row r="57" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C57" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -1653,20 +1695,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="G23:M23"/>
+    <mergeCell ref="G24:M24"/>
+    <mergeCell ref="G38:M38"/>
+    <mergeCell ref="G39:M39"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="G15:M15"/>
     <mergeCell ref="G16:M16"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="F1:L1"/>
-    <mergeCell ref="G23:M23"/>
-    <mergeCell ref="G24:M24"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C22:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="80">
   <si>
     <t>Name</t>
   </si>
@@ -105,9 +105,6 @@
     <t>Design</t>
   </si>
   <si>
-    <t>0, normal</t>
-  </si>
-  <si>
     <t>Red wooden barrel</t>
   </si>
   <si>
@@ -235,6 +232,30 @@
   </si>
   <si>
     <t>Applies "Protected" and "Enfeebled"</t>
+  </si>
+  <si>
+    <t>Teleportation rite</t>
+  </si>
+  <si>
+    <t>Create "Teleportation rite"</t>
+  </si>
+  <si>
+    <t>2x2</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Lightning</t>
+  </si>
+  <si>
+    <t>Teleportation beacon, Immovable</t>
+  </si>
+  <si>
+    <t>Stonehedge with cyan crystals and marks</t>
+  </si>
+  <si>
+    <t>Teleport rite</t>
   </si>
 </sst>
 </file>
@@ -784,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="4"/>
@@ -812,7 +833,7 @@
       <c r="D1" s="25"/>
       <c r="E1" s="25"/>
       <c r="F1" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
@@ -861,7 +882,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5"/>
       <c r="I5" s="7" t="s">
@@ -873,7 +894,7 @@
     </row>
     <row r="6" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" s="5"/>
       <c r="H6" s="5"/>
@@ -946,7 +967,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" s="5"/>
       <c r="H11" s="5"/>
@@ -1016,10 +1037,10 @@
         <v>27</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="M14" s="9">
         <v>15</v>
@@ -1033,7 +1054,7 @@
         <v>28</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" s="27"/>
       <c r="I15" s="27"/>
@@ -1049,7 +1070,7 @@
         <v>4</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H16" s="27"/>
       <c r="I16" s="27"/>
@@ -1068,14 +1089,14 @@
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -1083,14 +1104,14 @@
         <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.3">
@@ -1108,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="12" t="s">
@@ -1141,11 +1162,11 @@
         <v>6</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G22" s="12">
         <v>1</v>
@@ -1154,16 +1175,16 @@
         <v>0</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>27</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="M22" s="12">
         <v>15</v>
@@ -1177,7 +1198,7 @@
         <v>28</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H23" s="21"/>
       <c r="I23" s="21"/>
@@ -1194,7 +1215,7 @@
         <v>4</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="21"/>
@@ -1218,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -1232,7 +1253,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1276,14 +1297,14 @@
         <v>0</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="18" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -1297,14 +1318,14 @@
         <v>6</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="18" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -1357,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="16" t="s">
@@ -1390,29 +1411,29 @@
         <v>6</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G37" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H37" s="16" t="s">
-        <v>49</v>
-      </c>
       <c r="I37" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J37" s="16" t="s">
         <v>27</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M37" s="16">
         <v>20</v>
@@ -1426,7 +1447,7 @@
         <v>28</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H38" s="23"/>
       <c r="I38" s="23"/>
@@ -1443,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H39" s="23"/>
       <c r="I39" s="23"/>
@@ -1470,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -1487,7 +1508,7 @@
         <v>6</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -1517,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -1534,7 +1555,7 @@
         <v>6</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -1564,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -1581,7 +1602,7 @@
         <v>6</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -1593,7 +1614,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
     </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.3">
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -1601,51 +1622,51 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C50" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D50" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C51" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="3:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C51" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="16" t="s">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C53" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C53" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="15" t="s">
+      <c r="F53" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="G53" s="15" t="s">
+      <c r="F54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -1655,12 +1676,12 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
     </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C56" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
@@ -1669,12 +1690,12 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
     </row>
-    <row r="57" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C57" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
@@ -1683,7 +1704,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
     </row>
-    <row r="58" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -1693,8 +1714,102 @@
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
     </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C59" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C60" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G60" s="16">
+        <v>3</v>
+      </c>
+      <c r="H60" s="16">
+        <v>0</v>
+      </c>
+      <c r="I60" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J60" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M60" s="16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="F61" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H61" s="23"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="23"/>
+      <c r="K61" s="23"/>
+      <c r="L61" s="23"/>
+      <c r="M61" s="24"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="F62" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="H62" s="23"/>
+      <c r="I62" s="23"/>
+      <c r="J62" s="23"/>
+      <c r="K62" s="23"/>
+      <c r="L62" s="23"/>
+      <c r="M62" s="24"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
+    <mergeCell ref="G61:M61"/>
+    <mergeCell ref="G62:M62"/>
     <mergeCell ref="G23:M23"/>
     <mergeCell ref="G24:M24"/>
     <mergeCell ref="G38:M38"/>

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -467,16 +467,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -892,7 +892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
@@ -1161,7 +1161,7 @@
       <c r="C22" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="24" t="s">
         <v>36</v>
       </c>
       <c r="E22"/>
@@ -1192,37 +1192,37 @@
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C23" s="31"/>
-      <c r="D23" s="21"/>
+      <c r="D23" s="24"/>
       <c r="E23"/>
       <c r="F23" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="G23" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C24" s="31"/>
-      <c r="D24" s="21"/>
+      <c r="D24" s="24"/>
       <c r="E24"/>
       <c r="F24" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="21" t="s">
+      <c r="G24" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C25" s="5"/>
@@ -1252,7 +1252,7 @@
       <c r="C27" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="24" t="s">
         <v>59</v>
       </c>
       <c r="E27" s="5"/>
@@ -1264,7 +1264,7 @@
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C28" s="31"/>
-      <c r="D28" s="21"/>
+      <c r="D28" s="24"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="29" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C29" s="31"/>
-      <c r="D29" s="21"/>
+      <c r="D29" s="24"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -1446,15 +1446,15 @@
       <c r="F38" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="23"/>
-      <c r="L38" s="23"/>
-      <c r="M38" s="24"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="23"/>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C39" s="15"/>
@@ -1463,15 +1463,15 @@
       <c r="F39" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
-      <c r="L39" s="23"/>
-      <c r="M39" s="24"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="23"/>
     </row>
     <row r="40" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="5"/>
@@ -1782,48 +1782,48 @@
       <c r="F61" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G61" s="22" t="s">
+      <c r="G61" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H61" s="23"/>
-      <c r="I61" s="23"/>
-      <c r="J61" s="23"/>
-      <c r="K61" s="23"/>
-      <c r="L61" s="23"/>
-      <c r="M61" s="24"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+      <c r="M61" s="23"/>
     </row>
     <row r="62" spans="3:13" x14ac:dyDescent="0.3">
       <c r="F62" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="22" t="s">
+      <c r="G62" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="H62" s="23"/>
-      <c r="I62" s="23"/>
-      <c r="J62" s="23"/>
-      <c r="K62" s="23"/>
-      <c r="L62" s="23"/>
-      <c r="M62" s="24"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
+      <c r="M62" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G15:M15"/>
+    <mergeCell ref="G16:M16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="F1:L1"/>
     <mergeCell ref="G61:M61"/>
     <mergeCell ref="G62:M62"/>
     <mergeCell ref="G23:M23"/>
     <mergeCell ref="G24:M24"/>
     <mergeCell ref="G38:M38"/>
     <mergeCell ref="G39:M39"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G15:M15"/>
-    <mergeCell ref="G16:M16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="F1:L1"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="C22:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Items.xlsx
+++ b/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -138,9 +138,6 @@
     <t>Vulnerable:Fire, Explosive, Unscoring</t>
   </si>
   <si>
-    <t>Applies: Resistance:Fire, Weak:Lightning, If attacked by (Frost) damage, converts to Ice.  If attacked by (Fire) damage, disappears</t>
-  </si>
-  <si>
     <t>Small war hammer</t>
   </si>
   <si>
@@ -195,9 +192,6 @@
     <t>Applies "Polymorphed" to selected unit</t>
   </si>
   <si>
-    <t>Deal 3 (Physical) damage to the target</t>
-  </si>
-  <si>
     <t>At the end of the round, deals 3 (Lightning) damage to units on top</t>
   </si>
   <si>
@@ -256,6 +250,12 @@
   </si>
   <si>
     <t>Teleport rite</t>
+  </si>
+  <si>
+    <t>Applies: Resistance:Fire, Weak:Lightning, Frost. If attacked by (Frost) damage, converts to Ice.  If attacked by (Fire) damage, disappears</t>
+  </si>
+  <si>
+    <t>Deal 2 (Physical) damage to the target</t>
   </si>
 </sst>
 </file>
@@ -479,9 +479,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -495,6 +492,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
@@ -806,43 +806,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M62"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="8.85546875" style="4"/>
     <col min="2" max="2" width="5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="25.44140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="3.88671875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="46.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="40.44140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="32.44140625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" style="4"/>
-    <col min="13" max="13" width="5.109375" style="4" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="4"/>
+    <col min="3" max="3" width="7.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="46.28515625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="40.42578125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="32.42578125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" style="4"/>
+    <col min="13" max="13" width="5.140625" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+    </row>
+    <row r="4" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -867,7 +867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -882,7 +882,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="H5"/>
       <c r="I5" s="7" t="s">
@@ -892,7 +892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="46.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
@@ -901,7 +901,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,7 +922,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
         <v>6</v>
       </c>
@@ -940,7 +940,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9" s="5"/>
@@ -950,7 +950,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C10" s="6" t="s">
         <v>0</v>
       </c>
@@ -962,25 +962,25 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="28.9" x14ac:dyDescent="0.3">
       <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="E12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C13" s="6" t="s">
         <v>0</v>
       </c>
@@ -1013,11 +1013,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="30" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C14" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="29" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="5"/>
@@ -1037,54 +1037,54 @@
         <v>27</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M14" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C15" s="29"/>
-      <c r="D15" s="30"/>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C15" s="28"/>
+      <c r="D15" s="29"/>
       <c r="E15" s="5"/>
       <c r="F15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="28"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C16" s="29"/>
-      <c r="D16" s="30"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="27"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="C16" s="28"/>
+      <c r="D16" s="29"/>
       <c r="F16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="28"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="27"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="3:13" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:13" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="6" t="s">
         <v>0</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:13" ht="30" x14ac:dyDescent="0.25">
       <c r="C19" s="6" t="s">
         <v>6</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1124,7 +1124,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="3:13" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:13" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="11" t="s">
         <v>0</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:13" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="31" t="s">
         <v>6</v>
       </c>
@@ -1175,22 +1175,22 @@
         <v>0</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>27</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M22" s="12">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C23" s="31"/>
       <c r="D23" s="24"/>
       <c r="E23"/>
@@ -1207,7 +1207,7 @@
       <c r="L23" s="24"/>
       <c r="M23" s="24"/>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C24" s="31"/>
       <c r="D24" s="24"/>
       <c r="E24"/>
@@ -1224,7 +1224,7 @@
       <c r="L24" s="24"/>
       <c r="M24" s="24"/>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1234,12 +1234,12 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="3:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C26" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -1248,12 +1248,12 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C27" s="31" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1262,7 +1262,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C28" s="31"/>
       <c r="D28" s="24"/>
       <c r="E28" s="5"/>
@@ -1272,7 +1272,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C29" s="31"/>
       <c r="D29" s="24"/>
       <c r="E29" s="5"/>
@@ -1282,7 +1282,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="3:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -1292,19 +1292,19 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C31" s="18" t="s">
         <v>0</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="18" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -1313,19 +1313,19 @@
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
     </row>
-    <row r="32" spans="3:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:13" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="18" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="18" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -1334,7 +1334,7 @@
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
     </row>
-    <row r="33" spans="3:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:13" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1347,7 +1347,7 @@
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
     </row>
-    <row r="34" spans="3:13" ht="4.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:13" ht="4.1500000000000004" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -1360,7 +1360,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
     </row>
-    <row r="35" spans="3:13" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:13" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -1373,12 +1373,12 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
     </row>
-    <row r="36" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="16" t="s">
@@ -1406,40 +1406,40 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="3:13" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:13" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G37" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H37" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="H37" s="16" t="s">
-        <v>48</v>
-      </c>
       <c r="I37" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J37" s="16" t="s">
         <v>27</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M37" s="16">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C38" s="15"/>
       <c r="D38" s="16"/>
       <c r="E38" s="5"/>
@@ -1447,7 +1447,7 @@
         <v>28</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H38" s="22"/>
       <c r="I38" s="22"/>
@@ -1456,7 +1456,7 @@
       <c r="L38" s="22"/>
       <c r="M38" s="23"/>
     </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C39" s="15"/>
       <c r="D39" s="16"/>
       <c r="E39" s="5"/>
@@ -1464,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H39" s="22"/>
       <c r="I39" s="22"/>
@@ -1473,7 +1473,7 @@
       <c r="L39" s="22"/>
       <c r="M39" s="23"/>
     </row>
-    <row r="40" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -1486,12 +1486,12 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
     </row>
-    <row r="41" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -1503,12 +1503,12 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
     </row>
-    <row r="42" spans="3:13" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:13" ht="50.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -1520,7 +1520,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
     </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43" s="5"/>
@@ -1533,12 +1533,12 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
     </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C44" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -1550,12 +1550,12 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
     </row>
-    <row r="45" spans="3:13" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:13" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -1567,7 +1567,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
     </row>
-    <row r="46" spans="3:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46" s="5"/>
@@ -1580,12 +1580,12 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
     </row>
-    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -1597,12 +1597,12 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
     </row>
-    <row r="48" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:13" ht="30" x14ac:dyDescent="0.25">
       <c r="C48" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -1614,7 +1614,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.25">
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -1622,51 +1622,51 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C50" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D50" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="C51" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C53" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C51" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="16" t="s">
+      <c r="F53" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="C54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="16" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C53" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="G53" s="15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="3:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="16" t="s">
+      <c r="F54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -1676,12 +1676,12 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
     </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C56" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
@@ -1690,12 +1690,12 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
     </row>
-    <row r="57" spans="3:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:13" ht="30" x14ac:dyDescent="0.25">
       <c r="C57" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
@@ -1704,7 +1704,7 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
     </row>
-    <row r="58" spans="3:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -1714,12 +1714,12 @@
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C59" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F59" s="16" t="s">
         <v>0</v>
@@ -1746,15 +1746,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C60" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G60" s="16">
         <v>3</v>
@@ -1766,24 +1766,24 @@
         <v>26</v>
       </c>
       <c r="J60" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K60" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L60" s="16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M60" s="16">
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F61" s="16" t="s">
         <v>28</v>
       </c>
       <c r="G61" s="21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H61" s="22"/>
       <c r="I61" s="22"/>
@@ -1792,12 +1792,12 @@
       <c r="L61" s="22"/>
       <c r="M61" s="23"/>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.25">
       <c r="F62" s="16" t="s">
         <v>4</v>
       </c>
       <c r="G62" s="21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H62" s="22"/>
       <c r="I62" s="22"/>
@@ -1833,9 +1833,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1845,7 +1845,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
